--- a/assets/Design/02 资源字符串编辑.xlsx
+++ b/assets/Design/02 资源字符串编辑.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="131">
   <si>
     <t>Project</t>
   </si>
@@ -408,6 +408,18 @@
   </si>
   <si>
     <t>yyyy年MM月dd日 HH:mm</t>
+  </si>
+  <si>
+    <t>ArgumentException_invalid_typed_arguments</t>
+  </si>
+  <si>
+    <t>PLX0018: The parameter "{0}" is of the wrong type.</t>
+  </si>
+  <si>
+    <t>PLX0018: 错误类型的参数 “{0}”。</t>
+  </si>
+  <si>
+    <t>PLX0018: 錯誤類型的參數 “{0}”。</t>
   </si>
 </sst>
 </file>
@@ -1027,7 +1039,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
       <protection locked="0"/>
     </xf>
@@ -1036,6 +1048,9 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1571,7 +1586,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K31"/>
+  <dimension ref="A1:K32"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="28.3" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="17.875" style="1" customWidth="1"/>
@@ -2617,6 +2632,29 @@
         <v>126</v>
       </c>
     </row>
+    <row r="32" customHeight="1" spans="1:11">
+      <c r="A32" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="G32" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="K32" s="1" t="s">
+        <v>130</v>
+      </c>
+    </row>
   </sheetData>
   <sheetProtection formatColumns="0" formatRows="0" sort="0" autoFilter="0"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
